--- a/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
@@ -798,49 +798,49 @@
         </is>
       </c>
       <c r="B16" s="21" t="n">
-        <v>104247.5434</v>
+        <v>102780.6851</v>
       </c>
       <c r="C16" s="21" t="n">
-        <v>106437.275</v>
+        <v>103081.1032</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>110168.1339</v>
+        <v>104474.5979</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>115539.0836</v>
+        <v>107031.3611</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>122675.136</v>
+        <v>110840.0601</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>131714.4677</v>
+        <v>115998.6995</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>142759.3565</v>
+        <v>122579.822</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>155864.7106</v>
+        <v>130622.3724</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>171027.5473</v>
+        <v>140124.2351</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>188178.4383</v>
+        <v>151036.1666</v>
       </c>
       <c r="L16" s="21" t="n">
-        <v>207175.9358</v>
+        <v>163257.8423</v>
       </c>
       <c r="M16" s="21" t="n">
-        <v>227804.8743</v>
+        <v>176636.6514</v>
       </c>
       <c r="N16" s="21" t="n">
-        <v>250179.4547</v>
+        <v>191253.5933</v>
       </c>
       <c r="O16" s="21" t="n">
-        <v>274421.8718</v>
+        <v>207195.3372</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>300662.8743</v>
+        <v>224554.6194</v>
       </c>
     </row>
     <row r="17">
@@ -850,49 +850,49 @@
         </is>
       </c>
       <c r="B17" s="21" t="n">
-        <v>17695.9447</v>
+        <v>17446.9465</v>
       </c>
       <c r="C17" s="21" t="n">
-        <v>18067.65</v>
+        <v>17497.9423</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>18700.9606</v>
+        <v>17734.487</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>19612.6754</v>
+        <v>18168.4957</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>20824.0151</v>
+        <v>18815.0196</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>22358.4351</v>
+        <v>19690.6949</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>24233.297</v>
+        <v>20807.8356</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>26457.9213</v>
+        <v>22173.0527</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>29031.8018</v>
+        <v>23785.987</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>31943.1531</v>
+        <v>25638.2795</v>
       </c>
       <c r="L17" s="21" t="n">
-        <v>35167.9644</v>
+        <v>27712.9</v>
       </c>
       <c r="M17" s="21" t="n">
-        <v>38669.7118</v>
+        <v>29983.9431</v>
       </c>
       <c r="N17" s="21" t="n">
-        <v>42467.7805</v>
+        <v>32465.1584</v>
       </c>
       <c r="O17" s="21" t="n">
-        <v>46582.9132</v>
+        <v>35171.2578</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>51037.3043</v>
+        <v>38117.9833</v>
       </c>
     </row>
     <row r="18">
@@ -902,49 +902,49 @@
         </is>
       </c>
       <c r="B18" s="21" t="n">
-        <v>13013.9604</v>
+        <v>12830.8421</v>
       </c>
       <c r="C18" s="21" t="n">
-        <v>13287.3202</v>
+        <v>12868.3454</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>13753.0697</v>
+        <v>13042.3052</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>14423.5635</v>
+        <v>13361.4841</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>15314.4075</v>
+        <v>13836.951</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>16442.8514</v>
+        <v>14480.9406</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>17821.6633</v>
+        <v>15302.5088</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>19457.6976</v>
+        <v>16306.5174</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>21350.5821</v>
+        <v>17492.7024</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>23491.6495</v>
+        <v>18854.9162</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>25863.2419</v>
+        <v>20380.6347</v>
       </c>
       <c r="M18" s="21" t="n">
-        <v>28438.4986</v>
+        <v>22050.8063</v>
       </c>
       <c r="N18" s="21" t="n">
-        <v>31231.6762</v>
+        <v>23875.5429</v>
       </c>
       <c r="O18" s="21" t="n">
-        <v>34258.0291</v>
+        <v>25865.6639</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>37533.8796</v>
+        <v>28032.7462</v>
       </c>
     </row>
     <row r="19">
@@ -954,49 +954,49 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>9120.6492</v>
+        <v>8992.3133</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>9312.2294</v>
+        <v>9018.5969</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>9638.643400000001</v>
+        <v>9140.5142</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>10108.5494</v>
+        <v>9364.206200000001</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>10732.8848</v>
+        <v>9697.430399999999</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>11523.7387</v>
+        <v>10148.7614</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>12490.0594</v>
+        <v>10724.5458</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>13636.6508</v>
+        <v>11428.1909</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>14963.2519</v>
+        <v>12259.5118</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>16463.7886</v>
+        <v>13214.2</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>18125.8854</v>
+        <v>14283.4781</v>
       </c>
       <c r="M19" s="21" t="n">
-        <v>19930.7175</v>
+        <v>15453.9941</v>
       </c>
       <c r="N19" s="21" t="n">
-        <v>21888.2763</v>
+        <v>16732.8348</v>
       </c>
       <c r="O19" s="21" t="n">
-        <v>24009.2527</v>
+        <v>18127.5828</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>26305.086</v>
+        <v>19646.3517</v>
       </c>
     </row>
     <row r="20">
@@ -1162,49 +1162,49 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>176253.6456</v>
+        <v>174226.335</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>183280.226</v>
+        <v>178641.7393</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>193385.4107</v>
+        <v>185516.5074</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>206766.8924</v>
+        <v>195008.5676</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>223674.3988</v>
+        <v>207317.4165</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>244383.9558</v>
+        <v>222663.5593</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>269099.8767</v>
+        <v>241210.2129</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>297931.8479</v>
+        <v>263045.0012</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>330873.911</v>
+        <v>288163.1641</v>
       </c>
       <c r="K23" s="22" t="n">
-        <v>367787.3738</v>
+        <v>316453.9067</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>408389.676</v>
+        <v>347691.5035</v>
       </c>
       <c r="M23" s="22" t="n">
-        <v>452250.996</v>
+        <v>381532.5888</v>
       </c>
       <c r="N23" s="22" t="n">
-        <v>499599.4651</v>
+        <v>418159.4067</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>550679.1836</v>
+        <v>457766.9584</v>
       </c>
       <c r="P23" s="22" t="n">
-        <v>605751.339</v>
+        <v>500563.8955</v>
       </c>
     </row>
     <row r="24">
@@ -1214,49 +1214,49 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>69847.66379999999</v>
+        <v>68864.84329999999</v>
       </c>
       <c r="C24" s="21" t="n">
-        <v>71314.822</v>
+        <v>69066.1287</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>73814.56230000001</v>
+        <v>69999.79429999999</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>77413.1918</v>
+        <v>71712.87</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>82194.4708</v>
+        <v>74264.7645</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>88250.98</v>
+        <v>77721.1425</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>95651.2472</v>
+        <v>82130.6088</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>104432.062</v>
+        <v>87519.25719999999</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>114591.4258</v>
+        <v>93885.6701</v>
       </c>
       <c r="K24" s="21" t="n">
-        <v>126082.8205</v>
+        <v>101196.8537</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>138811.4737</v>
+        <v>109385.5886</v>
       </c>
       <c r="M24" s="21" t="n">
-        <v>152633.2206</v>
+        <v>118349.6229</v>
       </c>
       <c r="N24" s="21" t="n">
-        <v>167624.5779</v>
+        <v>128143.2277</v>
       </c>
       <c r="O24" s="21" t="n">
-        <v>183867.4182</v>
+        <v>138824.4729</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>201449.3454</v>
+        <v>150455.4934</v>
       </c>
     </row>
     <row r="25">
@@ -1266,49 +1266,49 @@
         </is>
       </c>
       <c r="B25" s="21" t="n">
-        <v>3834.0928</v>
+        <v>3780.1436</v>
       </c>
       <c r="C25" s="21" t="n">
-        <v>3914.6284</v>
+        <v>3791.1926</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>4051.8446</v>
+        <v>3842.4436</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>4249.3814</v>
+        <v>3936.4781</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>4511.8364</v>
+        <v>4076.5572</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>4844.2916</v>
+        <v>4266.2855</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>5250.5086</v>
+        <v>4508.3308</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>5732.5069</v>
+        <v>4804.1257</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>6290.1769</v>
+        <v>5153.5922</v>
       </c>
       <c r="K25" s="21" t="n">
-        <v>6920.965</v>
+        <v>5554.9192</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>7619.6689</v>
+        <v>6004.417</v>
       </c>
       <c r="M25" s="21" t="n">
-        <v>8378.3752</v>
+        <v>6496.4727</v>
       </c>
       <c r="N25" s="21" t="n">
-        <v>9201.284</v>
+        <v>7034.0653</v>
       </c>
       <c r="O25" s="21" t="n">
-        <v>10092.8894</v>
+        <v>7620.3825</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>11058.0003</v>
+        <v>8258.8349</v>
       </c>
     </row>
     <row r="26">
@@ -1318,49 +1318,49 @@
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>5158.149</v>
+        <v>5085.5691</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>5266.4965</v>
+        <v>5100.4337</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>5451.0987</v>
+        <v>5169.3836</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>5716.8523</v>
+        <v>5295.8918</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>6069.9428</v>
+        <v>5484.3455</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>6517.2073</v>
+        <v>5739.594</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>7063.7063</v>
+        <v>6065.2267</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>7712.1568</v>
+        <v>6463.1706</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>8462.411099999999</v>
+        <v>6933.321</v>
       </c>
       <c r="K26" s="21" t="n">
-        <v>9311.034</v>
+        <v>7473.2413</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>10251.0266</v>
+        <v>8077.9675</v>
       </c>
       <c r="M26" s="21" t="n">
-        <v>11271.7426</v>
+        <v>8739.9485</v>
       </c>
       <c r="N26" s="21" t="n">
-        <v>12378.8327</v>
+        <v>9463.1921</v>
       </c>
       <c r="O26" s="21" t="n">
-        <v>13578.343</v>
+        <v>10251.9866</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>14876.7429</v>
+        <v>11110.9206</v>
       </c>
     </row>
     <row r="27">
@@ -1370,49 +1370,49 @@
         </is>
       </c>
       <c r="B27" s="21" t="n">
-        <v>2471.1619</v>
+        <v>2436.3904</v>
       </c>
       <c r="C27" s="21" t="n">
-        <v>2523.069</v>
+        <v>2443.5118</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>2611.5081</v>
+        <v>2476.5442</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>2738.8251</v>
+        <v>2537.1516</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>2907.9834</v>
+        <v>2627.4359</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>3122.2585</v>
+        <v>2749.7202</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>3384.0748</v>
+        <v>2905.724</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>3694.734</v>
+        <v>3096.3707</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>4054.1652</v>
+        <v>3321.61</v>
       </c>
       <c r="K27" s="21" t="n">
-        <v>4460.7228</v>
+        <v>3580.2746</v>
       </c>
       <c r="L27" s="21" t="n">
-        <v>4911.0538</v>
+        <v>3869.9863</v>
       </c>
       <c r="M27" s="21" t="n">
-        <v>5400.0576</v>
+        <v>4187.1277</v>
       </c>
       <c r="N27" s="21" t="n">
-        <v>5930.4414</v>
+        <v>4533.6186</v>
       </c>
       <c r="O27" s="21" t="n">
-        <v>6505.1018</v>
+        <v>4911.5137</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>7127.1382</v>
+        <v>5323.0111</v>
       </c>
     </row>
     <row r="28">
@@ -1526,49 +1526,49 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>153938.5676</v>
+        <v>152794.4465</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>155646.5159</v>
+        <v>153028.7668</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>158556.5137</v>
+        <v>154115.6657</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>162745.7506</v>
+        <v>156109.8915</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>168311.7334</v>
+        <v>159080.6031</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>175362.2373</v>
+        <v>163104.2421</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>183977.037</v>
+        <v>168237.3904</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>194198.9597</v>
+        <v>174510.4241</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>206025.6791</v>
+        <v>181921.6932</v>
       </c>
       <c r="K30" s="22" t="n">
-        <v>219403.0423</v>
+        <v>190432.7888</v>
       </c>
       <c r="L30" s="22" t="n">
-        <v>234220.723</v>
+        <v>199965.4594</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>250310.896</v>
+        <v>210400.6718</v>
       </c>
       <c r="N30" s="22" t="n">
-        <v>267762.636</v>
+        <v>221801.6037</v>
       </c>
       <c r="O30" s="22" t="n">
-        <v>286671.2524</v>
+        <v>234235.8557</v>
       </c>
       <c r="P30" s="22" t="n">
-        <v>307138.7268</v>
+        <v>247775.76</v>
       </c>
     </row>
     <row r="31">
@@ -1578,49 +1578,49 @@
         </is>
       </c>
       <c r="B31" s="21" t="n">
-        <v>22315.078</v>
+        <v>21431.8885</v>
       </c>
       <c r="C31" s="21" t="n">
-        <v>27633.7101</v>
+        <v>25612.9725</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>34828.8971</v>
+        <v>31400.8418</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>44021.1419</v>
+        <v>38898.6761</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>55362.6654</v>
+        <v>48236.8134</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>69021.7185</v>
+        <v>59559.3171</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>85122.8397</v>
+        <v>72972.82249999999</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>103732.8882</v>
+        <v>88534.577</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>124848.2319</v>
+        <v>106241.4709</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>148384.3315</v>
+        <v>126021.1179</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>174168.953</v>
+        <v>147726.0441</v>
       </c>
       <c r="M31" s="21" t="n">
-        <v>201940.1</v>
+        <v>171131.9171</v>
       </c>
       <c r="N31" s="21" t="n">
-        <v>231836.8291</v>
+        <v>196357.803</v>
       </c>
       <c r="O31" s="21" t="n">
-        <v>264007.9311</v>
+        <v>223531.1028</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>298612.6121</v>
+        <v>252788.1354</v>
       </c>
     </row>
     <row r="32">
@@ -1630,49 +1630,49 @@
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>176253.6456</v>
+        <v>174226.335</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>183280.226</v>
+        <v>178641.7393</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>193385.4107</v>
+        <v>185516.5074</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>206766.8924</v>
+        <v>195008.5676</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>223674.3988</v>
+        <v>207317.4165</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>244383.9558</v>
+        <v>222663.5593</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>269099.8767</v>
+        <v>241210.2129</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>297931.8479</v>
+        <v>263045.0012</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>330873.911</v>
+        <v>288163.1641</v>
       </c>
       <c r="K32" s="22" t="n">
-        <v>367787.3738</v>
+        <v>316453.9067</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>408389.676</v>
+        <v>347691.5035</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>452250.996</v>
+        <v>381532.5888</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>499599.4651</v>
+        <v>418159.4067</v>
       </c>
       <c r="O32" s="22" t="n">
-        <v>550679.1836</v>
+        <v>457766.9584</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>605751.339</v>
+        <v>500563.8955</v>
       </c>
     </row>
     <row r="33">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="B33" s="27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C33" s="27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>-0</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F33" s="27" t="n">
         <v>-0</v>
@@ -1700,10 +1700,10 @@
         <v>-0</v>
       </c>
       <c r="H33" s="27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>-0</v>
@@ -1712,19 +1712,19 @@
         <v>0</v>
       </c>
       <c r="L33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="O33" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="N33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="27" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" s="27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
@@ -1734,49 +1734,49 @@
         </is>
       </c>
       <c r="B34" s="21" t="n">
-        <v>947.754</v>
+        <v>934.4182</v>
       </c>
       <c r="C34" s="21" t="n">
-        <v>751.2901000000001</v>
+        <v>727.6005</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>628.5612</v>
+        <v>596.0769</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>547.5124</v>
+        <v>507.1964</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>491.6721</v>
+        <v>444.2381</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>452.6288</v>
+        <v>398.6225</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>426.502</v>
+        <v>366.2145</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>410.5581</v>
+        <v>344.0681</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>402.8959</v>
+        <v>330.0958</v>
       </c>
       <c r="K34" s="21" t="n">
-        <v>402.2311</v>
+        <v>322.8396</v>
       </c>
       <c r="L34" s="21" t="n">
-        <v>407.7512</v>
+        <v>321.3143</v>
       </c>
       <c r="M34" s="21" t="n">
-        <v>419.0204</v>
+        <v>324.9025</v>
       </c>
       <c r="N34" s="21" t="n">
-        <v>430.0709</v>
+        <v>328.7744</v>
       </c>
       <c r="O34" s="21" t="n">
-        <v>440.883</v>
+        <v>332.8776</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>451.4406</v>
+        <v>337.1653</v>
       </c>
     </row>
     <row r="35">
@@ -1786,49 +1786,49 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>260.841</v>
+        <v>245.8561</v>
       </c>
       <c r="C35" s="21" t="n">
-        <v>206.7702</v>
+        <v>191.44</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>172.9927</v>
+        <v>156.8346</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>150.6865</v>
+        <v>133.4491</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>135.3181</v>
+        <v>116.8841</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>124.5726</v>
+        <v>104.8821</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>117.382</v>
+        <v>96.3552</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>112.9939</v>
+        <v>90.5282</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>110.8851</v>
+        <v>86.852</v>
       </c>
       <c r="K35" s="21" t="n">
-        <v>110.7021</v>
+        <v>84.94280000000001</v>
       </c>
       <c r="L35" s="21" t="n">
-        <v>112.2214</v>
+        <v>84.5414</v>
       </c>
       <c r="M35" s="21" t="n">
-        <v>115.3229</v>
+        <v>85.4855</v>
       </c>
       <c r="N35" s="21" t="n">
-        <v>118.3642</v>
+        <v>86.5043</v>
       </c>
       <c r="O35" s="21" t="n">
-        <v>121.3399</v>
+        <v>87.5839</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>124.2456</v>
+        <v>88.712</v>
       </c>
     </row>
     <row r="36">
@@ -1838,49 +1838,49 @@
         </is>
       </c>
       <c r="B36" s="21" t="n">
-        <v>56.5151</v>
+        <v>53.2684</v>
       </c>
       <c r="C36" s="21" t="n">
-        <v>44.7999</v>
+        <v>41.4783</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>37.4815</v>
+        <v>33.9806</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>32.6485</v>
+        <v>28.9138</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>29.3187</v>
+        <v>25.3247</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>26.9905</v>
+        <v>22.7243</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>25.4326</v>
+        <v>20.8768</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>24.4818</v>
+        <v>19.6143</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>24.0249</v>
+        <v>18.8178</v>
       </c>
       <c r="K36" s="21" t="n">
-        <v>23.9853</v>
+        <v>18.4041</v>
       </c>
       <c r="L36" s="21" t="n">
-        <v>24.3144</v>
+        <v>18.3172</v>
       </c>
       <c r="M36" s="21" t="n">
-        <v>24.9864</v>
+        <v>18.5217</v>
       </c>
       <c r="N36" s="21" t="n">
-        <v>25.6454</v>
+        <v>18.7425</v>
       </c>
       <c r="O36" s="21" t="n">
-        <v>26.2901</v>
+        <v>18.9764</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>26.9197</v>
+        <v>19.2208</v>
       </c>
     </row>
     <row r="37">
@@ -1890,49 +1890,49 @@
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>0.1981</v>
+        <v>0.1953</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>0.1599</v>
+        <v>0.1548</v>
       </c>
       <c r="D37" s="17" t="n">
-        <v>0.1366</v>
+        <v>0.1295</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0.1222</v>
+        <v>0.1132</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>0.1134</v>
+        <v>0.1025</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.1085</v>
+        <v>0.0955</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>0.1063</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>0.1061</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>0.1073</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>0.1094</v>
+        <v>0.0878</v>
       </c>
       <c r="L37" s="17" t="n">
-        <v>0.1119</v>
+        <v>0.0882</v>
       </c>
       <c r="M37" s="17" t="n">
-        <v>0.1143</v>
+        <v>0.0887</v>
       </c>
       <c r="N37" s="17" t="n">
-        <v>0.1168</v>
+        <v>0.0893</v>
       </c>
       <c r="O37" s="17" t="n">
-        <v>0.1191</v>
+        <v>0.09</v>
       </c>
       <c r="P37" s="17" t="n">
-        <v>0.1215</v>
+        <v>0.0907</v>
       </c>
     </row>
     <row r="38">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="B38" s="21" t="n">
-        <v>62767.03</v>
+        <v>61883.8405</v>
       </c>
       <c r="C38" s="21" t="n">
-        <v>64085.4587</v>
+        <v>62064.721</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>66331.79399999999</v>
+        <v>62903.7386</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>69565.6214</v>
+        <v>64443.1556</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>73862.2101</v>
+        <v>66736.3581</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>79304.7556</v>
+        <v>69842.35430000001</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>85954.8391</v>
+        <v>73804.8219</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>93845.5206</v>
+        <v>78647.20940000001</v>
       </c>
       <c r="J38" s="21" t="n">
-        <v>102975.004</v>
+        <v>84368.243</v>
       </c>
       <c r="K38" s="21" t="n">
-        <v>113301.4871</v>
+        <v>90938.2735</v>
       </c>
       <c r="L38" s="21" t="n">
-        <v>124739.8046</v>
+        <v>98296.8956</v>
       </c>
       <c r="M38" s="21" t="n">
-        <v>137160.4062</v>
+        <v>106352.2232</v>
       </c>
       <c r="N38" s="21" t="n">
-        <v>150632.0517</v>
+        <v>115153.0256</v>
       </c>
       <c r="O38" s="21" t="n">
-        <v>165228.3144</v>
+        <v>124751.4861</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>181027.9173</v>
+        <v>135203.4406</v>
       </c>
     </row>
     <row r="39">
@@ -1994,49 +1994,49 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>1.5634</v>
+        <v>1.5414</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>1.2393</v>
+        <v>1.2002</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.0369</v>
+        <v>0.9833</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.9032</v>
+        <v>0.8367</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.8111</v>
+        <v>0.7328</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0.7466</v>
+        <v>0.6576</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.7035</v>
+        <v>0.6041</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>0.6772</v>
+        <v>0.5676</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>0.6646</v>
+        <v>0.5445</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.6635</v>
+        <v>0.5325</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.6726</v>
+        <v>0.53</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.6912</v>
+        <v>0.536</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.7094</v>
+        <v>0.5423</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.5491</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.7447</v>
+        <v>0.5562</v>
       </c>
     </row>
     <row r="41">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B47" s="21" t="n">
-        <v>6104.3208</v>
+        <v>5221.1313</v>
       </c>
       <c r="C47" s="21" t="n">
         <v>2354.875</v>
@@ -2343,19 +2343,19 @@
         <v>2354.875</v>
       </c>
       <c r="L47" s="21" t="n">
-        <v>2779.3305</v>
+        <v>2354.875</v>
       </c>
       <c r="M47" s="21" t="n">
-        <v>8137.6202</v>
+        <v>3347.8907</v>
       </c>
       <c r="N47" s="21" t="n">
-        <v>14052.592</v>
+        <v>4592.0193</v>
       </c>
       <c r="O47" s="21" t="n">
-        <v>20563.2138</v>
+        <v>6104.8389</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>27711.1809</v>
+        <v>7905.1577</v>
       </c>
     </row>
     <row r="48">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="B50" s="22" t="n">
-        <v>184560.093</v>
+        <v>183676.9035</v>
       </c>
       <c r="C50" s="22" t="n">
         <v>226555.4955</v>
@@ -2499,19 +2499,19 @@
         <v>697636.2659</v>
       </c>
       <c r="L50" s="22" t="n">
-        <v>756220.4286</v>
+        <v>755795.9730999999</v>
       </c>
       <c r="M50" s="22" t="n">
-        <v>812969.3316</v>
+        <v>808179.6021</v>
       </c>
       <c r="N50" s="22" t="n">
-        <v>873872.2598</v>
+        <v>864411.6871</v>
       </c>
       <c r="O50" s="22" t="n">
-        <v>939219.9948</v>
+        <v>924761.6199</v>
       </c>
       <c r="P50" s="22" t="n">
-        <v>1009323.6732</v>
+        <v>989517.6499</v>
       </c>
     </row>
     <row r="51">
@@ -2732,46 +2732,46 @@
         <v>33552.7</v>
       </c>
       <c r="C55" s="21" t="n">
-        <v>44419.626</v>
+        <v>46440.3637</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>58369.2727</v>
+        <v>61797.328</v>
       </c>
       <c r="E55" s="21" t="n">
-        <v>71681.65429999999</v>
+        <v>76804.1201</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>84561.9237</v>
+        <v>91687.7757</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>97022.5762</v>
+        <v>106484.9775</v>
       </c>
       <c r="H55" s="21" t="n">
-        <v>108447.0381</v>
+        <v>120597.0553</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>118119.0533</v>
+        <v>133317.3644</v>
       </c>
       <c r="J55" s="21" t="n">
-        <v>125248.494</v>
+        <v>143855.255</v>
       </c>
       <c r="K55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>151371.9443</v>
       </c>
       <c r="L55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>155027.1841</v>
       </c>
       <c r="M55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>155027.1841</v>
       </c>
       <c r="N55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>155027.1841</v>
       </c>
       <c r="O55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>155027.1841</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>129008.7307</v>
+        <v>155027.1841</v>
       </c>
     </row>
     <row r="56">
@@ -2836,46 +2836,46 @@
         <v>162245.015</v>
       </c>
       <c r="C57" s="22" t="n">
-        <v>198921.7853</v>
+        <v>200942.523</v>
       </c>
       <c r="D57" s="22" t="n">
-        <v>240245.0303</v>
+        <v>243673.0856</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>282688.8073</v>
+        <v>287811.273</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>326920.9412</v>
+        <v>334046.7932</v>
       </c>
       <c r="G57" s="22" t="n">
-        <v>373187.7591</v>
+        <v>382650.1604</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>420235.051</v>
+        <v>432385.0682</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>466505.1793</v>
+        <v>481703.4905</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>510179.7532</v>
+        <v>528786.5142</v>
       </c>
       <c r="K57" s="22" t="n">
-        <v>549251.9344</v>
+        <v>571615.148</v>
       </c>
       <c r="L57" s="22" t="n">
-        <v>582051.4754999999</v>
+        <v>608069.929</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>611029.2316000001</v>
+        <v>637047.6851</v>
       </c>
       <c r="N57" s="22" t="n">
-        <v>642035.4307</v>
+        <v>668053.8842</v>
       </c>
       <c r="O57" s="22" t="n">
-        <v>675212.0637000001</v>
+        <v>701230.5172</v>
       </c>
       <c r="P57" s="22" t="n">
-        <v>710711.061</v>
+        <v>736729.5145</v>
       </c>
     </row>
     <row r="58">
@@ -2885,49 +2885,49 @@
         </is>
       </c>
       <c r="B58" s="21" t="n">
-        <v>22315.078</v>
+        <v>21431.8885</v>
       </c>
       <c r="C58" s="21" t="n">
-        <v>27633.7101</v>
+        <v>25612.9725</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>34828.8971</v>
+        <v>31400.8418</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>44021.1419</v>
+        <v>38898.6761</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>55362.6654</v>
+        <v>48236.8134</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>69021.7185</v>
+        <v>59559.3171</v>
       </c>
       <c r="H58" s="21" t="n">
-        <v>85122.8397</v>
+        <v>72972.82249999999</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>103732.8882</v>
+        <v>88534.577</v>
       </c>
       <c r="J58" s="21" t="n">
-        <v>124848.2319</v>
+        <v>106241.4709</v>
       </c>
       <c r="K58" s="21" t="n">
-        <v>148384.3315</v>
+        <v>126021.1179</v>
       </c>
       <c r="L58" s="21" t="n">
-        <v>174168.953</v>
+        <v>147726.0441</v>
       </c>
       <c r="M58" s="21" t="n">
-        <v>201940.1</v>
+        <v>171131.9171</v>
       </c>
       <c r="N58" s="21" t="n">
-        <v>231836.8291</v>
+        <v>196357.803</v>
       </c>
       <c r="O58" s="21" t="n">
-        <v>264007.9311</v>
+        <v>223531.1028</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>298612.6121</v>
+        <v>252788.1354</v>
       </c>
     </row>
     <row r="59">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B59" s="22" t="n">
-        <v>184560.093</v>
+        <v>183676.9035</v>
       </c>
       <c r="C59" s="22" t="n">
         <v>226555.4955</v>
@@ -2967,19 +2967,19 @@
         <v>697636.2659</v>
       </c>
       <c r="L59" s="22" t="n">
-        <v>756220.4286</v>
+        <v>755795.9730999999</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>812969.3316</v>
+        <v>808179.6021</v>
       </c>
       <c r="N59" s="22" t="n">
-        <v>873872.2598</v>
+        <v>864411.6871</v>
       </c>
       <c r="O59" s="22" t="n">
-        <v>939219.9948</v>
+        <v>924761.6199</v>
       </c>
       <c r="P59" s="22" t="n">
-        <v>1009323.6732</v>
+        <v>989517.6499</v>
       </c>
     </row>
     <row r="60">
@@ -3007,10 +3007,10 @@
         <v>-0</v>
       </c>
       <c r="H60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="27" t="n">
         <v>-0</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>0</v>
       </c>
       <c r="J60" s="27" t="n">
         <v>-0</v>
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="L60" s="27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N60" s="27" t="n">
         <v>-0</v>
@@ -3093,49 +3093,49 @@
         </is>
       </c>
       <c r="B62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="C62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="H62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="J62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="K62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="L62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="M62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="N62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="O62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
       <c r="P62" s="21" t="n">
-        <v>287.4876</v>
+        <v>274.8391</v>
       </c>
     </row>
     <row r="63">
@@ -3145,49 +3145,49 @@
         </is>
       </c>
       <c r="B63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="C63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="H63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="J63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="K63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="L63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="M63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="N63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="O63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>62.2885</v>
+        <v>59.548</v>
       </c>
     </row>
     <row r="64">
@@ -3556,49 +3556,49 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>3549.278</v>
+        <v>2666.0885</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>5318.6321</v>
+        <v>4181.084</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>7195.1869</v>
+        <v>5787.8693</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>9192.2448</v>
+        <v>7497.8343</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>11341.5235</v>
+        <v>9338.1373</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>13659.0531</v>
+        <v>11322.5037</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>16101.1212</v>
+        <v>13413.5054</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>18610.0485</v>
+        <v>15561.7545</v>
       </c>
       <c r="J6" s="21" t="n">
-        <v>21115.3437</v>
+        <v>17706.8938</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>23536.0996</v>
+        <v>19779.647</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>25784.6216</v>
+        <v>21704.9262</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>27771.1469</v>
+        <v>23405.8729</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>29896.7291</v>
+        <v>25225.8859</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>32171.102</v>
+        <v>27173.2998</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>34604.681</v>
+        <v>29257.0327</v>
       </c>
     </row>
     <row r="7">
@@ -3660,49 +3660,49 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>-443.53</v>
+        <v>439.6595</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>-1318.4287</v>
+        <v>-180.8806</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>-2246.3353</v>
+        <v>-839.0176</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>-3233.8274</v>
+        <v>-1539.4169</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>-4296.5887</v>
+        <v>-2293.2025</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-5442.5456</v>
+        <v>-3105.9962</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>-6650.0835</v>
+        <v>-3962.4676</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>-7890.6814</v>
+        <v>-4842.3875</v>
       </c>
       <c r="J8" s="21" t="n">
-        <v>-9129.4835</v>
+        <v>-5721.0336</v>
       </c>
       <c r="K8" s="21" t="n">
-        <v>-10326.483</v>
+        <v>-6570.0305</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>-11438.3175</v>
+        <v>-7358.6222</v>
       </c>
       <c r="M8" s="21" t="n">
-        <v>-12420.6016</v>
+        <v>-8055.3276</v>
       </c>
       <c r="N8" s="21" t="n">
-        <v>-13471.6456</v>
+        <v>-8800.8024</v>
       </c>
       <c r="O8" s="21" t="n">
-        <v>-14596.2626</v>
+        <v>-9598.4604</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>-15799.6029</v>
+        <v>-10451.9545</v>
       </c>
     </row>
     <row r="9">
@@ -4135,49 +4135,49 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>3549.278</v>
+        <v>2666.0885</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>5318.6321</v>
+        <v>4181.084</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>7195.1869</v>
+        <v>5787.8693</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>9192.2448</v>
+        <v>7497.8343</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>11341.5235</v>
+        <v>9338.1373</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>13659.0531</v>
+        <v>11322.5037</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>16101.1212</v>
+        <v>13413.5054</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>18610.0485</v>
+        <v>15561.7545</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>21115.3437</v>
+        <v>17706.8938</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>23536.0996</v>
+        <v>19779.647</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>25784.6216</v>
+        <v>21704.9262</v>
       </c>
       <c r="M19" s="21" t="n">
-        <v>27771.1469</v>
+        <v>23405.8729</v>
       </c>
       <c r="N19" s="21" t="n">
-        <v>29896.7291</v>
+        <v>25225.8859</v>
       </c>
       <c r="O19" s="21" t="n">
-        <v>32171.102</v>
+        <v>27173.2998</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>34604.681</v>
+        <v>29257.0327</v>
       </c>
     </row>
     <row r="20">
@@ -4291,49 +4291,49 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>-2913.7</v>
+        <v>-3796.8895</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>-14099.2666</v>
+        <v>-15236.8147</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>-13309.9099</v>
+        <v>-14717.2276</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>-12542.1386</v>
+        <v>-14236.549</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>-11969.5725</v>
+        <v>-13972.9587</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>-11398.5068</v>
+        <v>-13735.0561</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>-10202.7287</v>
+        <v>-12890.3446</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>-8286.3254</v>
+        <v>-11334.6194</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>-5580.0317</v>
+        <v>-8988.481599999999</v>
       </c>
       <c r="K22" s="22" t="n">
-        <v>-2052.633</v>
+        <v>-5809.0856</v>
       </c>
       <c r="L22" s="22" t="n">
-        <v>2278.9985</v>
+        <v>-1800.6969</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>7342.6507</v>
+        <v>2977.3767</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>8038.2381</v>
+        <v>3367.3949</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>8782.516600000001</v>
+        <v>3784.7144</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>9578.894700000001</v>
+        <v>4231.2463</v>
       </c>
     </row>
     <row r="23">
@@ -4343,49 +4343,49 @@
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>-0.0726</v>
+        <v>-0.0946</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>-0.2727</v>
+        <v>-0.2947</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>-0.2081</v>
+        <v>-0.2301</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.1628</v>
+        <v>-0.1848</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>-0.1314</v>
+        <v>-0.1534</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>-0.1073</v>
+        <v>-0.1293</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>-0.0835</v>
+        <v>-0.1055</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-0.0598</v>
+        <v>-0.0818</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>-0.036</v>
+        <v>-0.058</v>
       </c>
       <c r="K23" s="17" t="n">
-        <v>-0.012</v>
+        <v>-0.034</v>
       </c>
       <c r="L23" s="17" t="n">
-        <v>0.0123</v>
+        <v>-0.0097</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>0.037</v>
+        <v>0.015</v>
       </c>
       <c r="N23" s="17" t="n">
-        <v>0.0379</v>
+        <v>0.0159</v>
       </c>
       <c r="O23" s="17" t="n">
-        <v>0.0387</v>
+        <v>0.0167</v>
       </c>
       <c r="P23" s="17" t="n">
-        <v>0.0394</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="24">
@@ -4450,34 +4450,34 @@
         <v>0</v>
       </c>
       <c r="C25" s="21" t="n">
-        <v>10866.926</v>
+        <v>12887.6637</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>13949.6467</v>
+        <v>15356.9644</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>13312.3816</v>
+        <v>15006.7921</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>12880.2694</v>
+        <v>14883.6556</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>12460.6525</v>
+        <v>14797.2019</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>11424.4619</v>
+        <v>14112.0778</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>9672.0152</v>
+        <v>12720.3091</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>7129.4407</v>
+        <v>10537.8906</v>
       </c>
       <c r="K25" s="21" t="n">
-        <v>3760.2366</v>
+        <v>7516.6892</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>0</v>
+        <v>3655.2398</v>
       </c>
       <c r="M25" s="21" t="n">
         <v>0</v>
@@ -4502,34 +4502,34 @@
         <v>0</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>10866.926</v>
+        <v>12887.6637</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>13949.6467</v>
+        <v>15356.9644</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>13312.3816</v>
+        <v>15006.7921</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>12880.2694</v>
+        <v>14883.6556</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>12460.6525</v>
+        <v>14797.2019</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>11424.4619</v>
+        <v>14112.0778</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>9672.0152</v>
+        <v>12720.3091</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>7129.4407</v>
+        <v>10537.8906</v>
       </c>
       <c r="K26" s="21" t="n">
-        <v>3760.2366</v>
+        <v>7516.6892</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>0</v>
+        <v>3655.2398</v>
       </c>
       <c r="M26" s="21" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>6104.3208</v>
+        <v>5221.1313</v>
       </c>
       <c r="C27" s="22" t="n">
         <v>2354.875</v>
@@ -4581,19 +4581,19 @@
         <v>2354.875</v>
       </c>
       <c r="L27" s="22" t="n">
-        <v>2779.3305</v>
+        <v>2354.875</v>
       </c>
       <c r="M27" s="22" t="n">
-        <v>8137.6202</v>
+        <v>3347.8907</v>
       </c>
       <c r="N27" s="22" t="n">
-        <v>14052.592</v>
+        <v>4592.0193</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>20563.2138</v>
+        <v>6104.8389</v>
       </c>
       <c r="P27" s="22" t="n">
-        <v>27711.1809</v>
+        <v>7905.1577</v>
       </c>
     </row>
     <row r="28">
@@ -4606,46 +4606,46 @@
         <v>0</v>
       </c>
       <c r="C28" s="21" t="n">
-        <v>10866.926</v>
+        <v>12887.6637</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>24816.5727</v>
+        <v>28244.628</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>38128.9543</v>
+        <v>43251.4201</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>51009.2237</v>
+        <v>58135.0757</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>63469.8762</v>
+        <v>72932.2775</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>74894.33809999999</v>
+        <v>87044.3553</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>84566.3533</v>
+        <v>99764.66439999999</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>91695.79399999999</v>
+        <v>110302.555</v>
       </c>
       <c r="K28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>117819.2443</v>
       </c>
       <c r="L28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>121474.4841</v>
       </c>
       <c r="M28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>121474.4841</v>
       </c>
       <c r="N28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>121474.4841</v>
       </c>
       <c r="O28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>121474.4841</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>95456.0307</v>
+        <v>121474.4841</v>
       </c>
     </row>
     <row r="30">
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>7.45</v>
+        <v>5.59</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>11.17</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>17.37</v>
+        <v>13.05</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -8575,49 +8575,49 @@
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>12.1676</v>
+        <v>12.7276</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>13.6278</v>
+        <v>14.2549</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>14.8543</v>
+        <v>15.5379</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>15.9683</v>
+        <v>16.7032</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>17.0861</v>
+        <v>17.8724</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>18.2821</v>
+        <v>19.1235</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>19.5619</v>
+        <v>20.4622</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>20.9312</v>
+        <v>21.8945</v>
       </c>
       <c r="J10" s="25" t="n">
-        <v>22.3964</v>
+        <v>23.4271</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>23.9642</v>
+        <v>25.067</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>25.6416</v>
+        <v>26.8217</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>27.4366</v>
+        <v>28.6992</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>29.3571</v>
+        <v>30.7082</v>
       </c>
       <c r="O10" s="25" t="n">
-        <v>31.4121</v>
+        <v>32.8578</v>
       </c>
       <c r="P10" s="25" t="n">
-        <v>33.611</v>
+        <v>35.1578</v>
       </c>
     </row>
     <row r="11">
@@ -8627,49 +8627,49 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>24762.2864</v>
+        <v>25901.8858</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>31893.8249</v>
+        <v>33361.6289</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>39457.4455</v>
+        <v>41273.3392</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>47506.7643</v>
+        <v>49693.1004</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>56169.6228</v>
+        <v>58754.6373</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>65510.6311</v>
+        <v>68525.53350000001</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>75353.60340000001</v>
+        <v>78821.49490000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>85466.057</v>
+        <v>89399.3395</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>95563.8716</v>
+        <v>99961.8714</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>105320.9429</v>
+        <v>110167.9785</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>114383.81</v>
+        <v>119647.9331</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>122390.6767</v>
+        <v>128023.2884</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>130958.0241</v>
+        <v>136984.9185</v>
       </c>
       <c r="O11" s="24" t="n">
-        <v>140125.0858</v>
+        <v>146573.8628</v>
       </c>
       <c r="P11" s="24" t="n">
-        <v>149933.8418</v>
+        <v>156834.0332</v>
       </c>
     </row>
     <row r="12">
@@ -8679,49 +8679,49 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>15385.6366</v>
+        <v>14246.0372</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>19816.6999</v>
+        <v>18348.8959</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>24516.2303</v>
+        <v>22700.3366</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>29517.5413</v>
+        <v>27331.2052</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>34900.065</v>
+        <v>32315.0505</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>40703.9458</v>
+        <v>37689.0434</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>46819.7136</v>
+        <v>43351.8222</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>53102.9192</v>
+        <v>49169.6367</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>59377.0291</v>
+        <v>54979.0293</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>65439.4238</v>
+        <v>60592.3882</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>71070.4862</v>
+        <v>65806.36320000001</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>76045.42019999999</v>
+        <v>70412.8086</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>81368.5996</v>
+        <v>75341.7052</v>
       </c>
       <c r="O12" s="24" t="n">
-        <v>87064.4016</v>
+        <v>80615.6246</v>
       </c>
       <c r="P12" s="24" t="n">
-        <v>93158.9097</v>
+        <v>86258.71829999999</v>
       </c>
     </row>
     <row r="13">
@@ -8731,49 +8731,49 @@
         </is>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="C13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="I13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="J13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="K13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="L13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
       <c r="P13" s="26" t="n">
-        <v>0.3832</v>
+        <v>0.3548</v>
       </c>
     </row>
     <row r="14">
@@ -8835,49 +8835,49 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>7927.2136</v>
+        <v>6787.6142</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>10210.2511</v>
+        <v>8742.447099999999</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>12631.6122</v>
+        <v>10815.7184</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>15208.461</v>
+        <v>13022.125</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>17981.7239</v>
+        <v>15396.7094</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>20972.0846</v>
+        <v>17957.1822</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>24123.1403</v>
+        <v>20655.2489</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>27360.4657</v>
+        <v>23427.1833</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>30593.1048</v>
+        <v>26195.105</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>33716.6608</v>
+        <v>28869.6252</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>36617.9794</v>
+        <v>31353.8564</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>39181.238</v>
+        <v>33548.6264</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>41923.9247</v>
+        <v>35897.0302</v>
       </c>
       <c r="O15" s="24" t="n">
-        <v>44858.5994</v>
+        <v>38409.8223</v>
       </c>
       <c r="P15" s="24" t="n">
-        <v>47998.7013</v>
+        <v>41098.5099</v>
       </c>
     </row>
     <row r="16">
@@ -8939,49 +8939,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>4579.7136</v>
+        <v>3440.1142</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>6862.7511</v>
+        <v>5394.9471</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>9284.1122</v>
+        <v>7468.2184</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>11860.961</v>
+        <v>9674.625</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>14634.2239</v>
+        <v>12049.2094</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>17624.5846</v>
+        <v>14609.6822</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>20775.6403</v>
+        <v>17307.7489</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>24012.9657</v>
+        <v>20079.6833</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>27245.6048</v>
+        <v>22847.605</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>30369.1608</v>
+        <v>25522.1252</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>33270.4794</v>
+        <v>28006.3564</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>35833.738</v>
+        <v>30201.1264</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>38576.4247</v>
+        <v>32549.5302</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>41511.0994</v>
+        <v>35062.3223</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>44651.2013</v>
+        <v>37751.0099</v>
       </c>
     </row>
     <row r="18">
@@ -8991,49 +8991,49 @@
         </is>
       </c>
       <c r="B18" s="24" t="n">
-        <v>3549.278</v>
+        <v>2666.0885</v>
       </c>
       <c r="C18" s="24" t="n">
-        <v>5318.6321</v>
+        <v>4181.084</v>
       </c>
       <c r="D18" s="24" t="n">
-        <v>7195.1869</v>
+        <v>5787.8693</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>9192.2448</v>
+        <v>7497.8343</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>11341.5235</v>
+        <v>9338.1373</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>13659.0531</v>
+        <v>11322.5037</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>16101.1212</v>
+        <v>13413.5054</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>18610.0485</v>
+        <v>15561.7545</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>21115.3437</v>
+        <v>17706.8938</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>23536.0996</v>
+        <v>19779.647</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>25784.6216</v>
+        <v>21704.9262</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>27771.1469</v>
+        <v>23405.8729</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>29896.7291</v>
+        <v>25225.8859</v>
       </c>
       <c r="O18" s="24" t="n">
-        <v>32171.102</v>
+        <v>27173.2998</v>
       </c>
       <c r="P18" s="24" t="n">
-        <v>34604.681</v>
+        <v>29257.0327</v>
       </c>
     </row>
     <row r="19">
@@ -9043,49 +9043,49 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>1.241</v>
+        <v>0.9322</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>1.8597</v>
+        <v>1.462</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>2.5159</v>
+        <v>2.0238</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>3.2142</v>
+        <v>2.6217</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>3.9657</v>
+        <v>3.2652</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>4.776</v>
+        <v>3.959</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>5.6299</v>
+        <v>4.6902</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>6.5072</v>
+        <v>5.4413</v>
       </c>
       <c r="J19" s="25" t="n">
-        <v>7.3832</v>
+        <v>6.1914</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>8.2296</v>
+        <v>6.9162</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>9.0159</v>
+        <v>7.5893</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>9.7105</v>
+        <v>8.184100000000001</v>
       </c>
       <c r="N19" s="25" t="n">
-        <v>10.4537</v>
+        <v>8.820499999999999</v>
       </c>
       <c r="O19" s="25" t="n">
-        <v>11.249</v>
+        <v>9.5014</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>12.0999</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="20">

--- a/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
@@ -5103,19 +5103,19 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>0.2110848413262307</v>
+        <v>0.2110196958005933</v>
       </c>
       <c r="C4" s="29" t="n">
-        <v>0.2310848413262307</v>
+        <v>0.2310196958005933</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>0.2510848413262307</v>
+        <v>0.2510196958005933</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>0.2710848413262307</v>
+        <v>0.2710196958005933</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>0.2910848413262307</v>
+        <v>0.2910196958005933</v>
       </c>
     </row>
     <row r="5">
@@ -5123,16 +5123,16 @@
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>15.25</v>
+        <v>15.27</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>2.52</v>
@@ -5143,13 +5143,13 @@
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>24.81</v>
+        <v>24.84</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>16.1</v>
+        <v>16.12</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>11.2</v>
+        <v>11.21</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>8.050000000000001</v>
@@ -5163,19 +5163,19 @@
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>37.4</v>
+        <v>37.44</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>24.88</v>
+        <v>24.9</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>13.36</v>
+        <v>13.37</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="8">
@@ -5183,19 +5183,19 @@
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.64</v>
+        <v>52.7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35.5</v>
+        <v>35.53</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>25.9</v>
+        <v>25.92</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>19.78</v>
+        <v>19.8</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="9">
@@ -5203,19 +5203,19 @@
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>79.86</v>
+        <v>79.95</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>31.27</v>
+        <v>31.29</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
     </row>
   </sheetData>
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46.5</v>
+        <v>46.53</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -5723,13 +5723,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>46.5</v>
+        <v>46.53</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1</v>
@@ -5764,13 +5764,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>17565</v>
+        <v>17584</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>36814</v>
+        <v>36833</v>
       </c>
     </row>
     <row r="12">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>51043</v>
+        <v>51083</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>71937</v>
+        <v>71979</v>
       </c>
     </row>
     <row r="13">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>115225</v>
+        <v>115306</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>139273</v>
+        <v>139357</v>
       </c>
     </row>
     <row r="14">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17.46</v>
+        <v>17.47</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>49934</v>
+        <v>49977</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>70773</v>
+        <v>70818</v>
       </c>
     </row>
     <row r="16">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.0731</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="20">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.2609671471091543</v>
+        <v>0.2608706403474768</v>
       </c>
     </row>
     <row r="22">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.2510848413262307</v>
+        <v>0.2510196958005933</v>
       </c>
     </row>
     <row r="23">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>49462.4</v>
+        <v>49477.7</v>
       </c>
     </row>
     <row r="5">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>22474.6</v>
+        <v>22501.1</v>
       </c>
     </row>
     <row r="6">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.2609671471091543</v>
+        <v>0.2608706403474768</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>71936.89999999999</v>
+        <v>71978.8</v>
       </c>
     </row>
     <row r="5">
@@ -8009,49 +8009,49 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0.251085</v>
+        <v>0.25102</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.219107</v>
+        <v>0.219048</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.193525</v>
+        <v>0.19347</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.174338</v>
+        <v>0.174287</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
     </row>
     <row r="17">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>22474.6</v>
+        <v>22501.1</v>
       </c>
     </row>
     <row r="22">

--- a/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>1.4718</v>
+        <v>1.4687</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>0.3261</v>
+        <v>0.3252</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>0.1848</v>
+        <v>0.1833</v>
       </c>
       <c r="F5" s="26" t="n">
         <v>0.4394</v>
@@ -5446,13 +5446,13 @@
         </is>
       </c>
       <c r="C6" s="31" t="n">
-        <v>1.0493</v>
+        <v>1.0481</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.2988</v>
+        <v>0.2997</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>0.1823</v>
+        <v>0.1808</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>0.4391</v>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.8837</v>
+        <v>0.8817</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>0.321</v>
+        <v>0.3251</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>0.173</v>
+        <v>0.1727</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>0.4636</v>
+        <v>0.4619</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>-0.4293</v>
@@ -5500,13 +5500,13 @@
         </is>
       </c>
       <c r="C8" s="31" t="n">
-        <v>0.7653</v>
+        <v>0.7648</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>0.2884</v>
+        <v>0.2874</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>0.1815</v>
+        <v>0.1803</v>
       </c>
       <c r="F8" s="26" t="n">
         <v>0.444</v>
@@ -5527,16 +5527,16 @@
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.7388</v>
+        <v>0.7349</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>0.2441</v>
+        <v>0.2423</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>0.1692</v>
+        <v>0.1693</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>0.4106</v>
+        <v>0.412</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>-0.4712</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>0.7067</v>
+        <v>0.7006</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>0.2576</v>
+        <v>0.2565</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>0.1864</v>
+        <v>0.1854</v>
       </c>
       <c r="F10" s="26" t="n">
         <v>0.4217</v>
@@ -5581,16 +5581,16 @@
         </is>
       </c>
       <c r="C11" s="31" t="n">
-        <v>0.4938</v>
+        <v>0.4949</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>0.1033</v>
+        <v>0.1018</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>0.2237</v>
+        <v>0.2275</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>0.4713</v>
+        <v>0.4755</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>-0.4658</v>

--- a/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_03092026.xlsx
@@ -5103,19 +5103,19 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>0.2110196958005933</v>
+        <v>0.209647238833035</v>
       </c>
       <c r="C4" s="29" t="n">
-        <v>0.2310196958005933</v>
+        <v>0.229647238833035</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>0.2510196958005933</v>
+        <v>0.249647238833035</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>0.2710196958005933</v>
+        <v>0.269647238833035</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>0.2910196958005933</v>
+        <v>0.2896472388330349</v>
       </c>
     </row>
     <row r="5">
@@ -5123,19 +5123,19 @@
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>15.27</v>
+        <v>20.9</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>9.449999999999999</v>
+        <v>12.08</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6.15</v>
+        <v>7.65</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4.02</v>
+        <v>4.98</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2.52</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="6">
@@ -5143,19 +5143,19 @@
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>24.84</v>
+        <v>33.33</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>16.12</v>
+        <v>20.07</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>11.21</v>
+        <v>13.45</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>8.050000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.86</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="7">
@@ -5163,19 +5163,19 @@
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>37.44</v>
+        <v>49.69</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>24.9</v>
+        <v>30.59</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>17.86</v>
+        <v>21.09</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>13.37</v>
+        <v>15.42</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>10.25</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="8">
@@ -5183,19 +5183,19 @@
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.7</v>
+        <v>69.5</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35.53</v>
+        <v>43.32</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>25.92</v>
+        <v>30.34</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>19.8</v>
+        <v>22.6</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>15.57</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="9">
@@ -5203,19 +5203,19 @@
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>79.95</v>
+        <v>104.89</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>54.52</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>40.32</v>
+        <v>46.85</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>31.29</v>
+        <v>35.43</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25.06</v>
+        <v>27.89</v>
       </c>
     </row>
   </sheetData>
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4.02</v>
+        <v>4.98</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>17.86</v>
+        <v>21.09</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46.53</v>
+        <v>55.07</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -5723,13 +5723,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4.02</v>
+        <v>4.98</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>17.86</v>
+        <v>21.09</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>46.53</v>
+        <v>55.07</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1</v>
@@ -5764,13 +5764,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>6.15</v>
+        <v>7.65</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>17584</v>
+        <v>21883</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>36833</v>
+        <v>41344</v>
       </c>
     </row>
     <row r="12">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>17.86</v>
+        <v>21.09</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>51083</v>
+        <v>60315</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>71979</v>
+        <v>81664</v>
       </c>
     </row>
     <row r="13">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>40.32</v>
+        <v>46.85</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>115306</v>
+        <v>133993</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>139357</v>
+        <v>158963</v>
       </c>
     </row>
     <row r="14">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17.47</v>
+        <v>20.7</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>49977</v>
+        <v>59192</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>70818</v>
+        <v>80486</v>
       </c>
     </row>
     <row r="16">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.073</v>
+        <v>0.0634</v>
       </c>
     </row>
     <row r="20">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>49477.7</v>
+        <v>52181.7</v>
       </c>
     </row>
     <row r="5">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>22501.1</v>
+        <v>29482.4</v>
       </c>
     </row>
     <row r="6">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>71978.8</v>
+        <v>81664.10000000001</v>
       </c>
     </row>
     <row r="5">
@@ -8009,49 +8009,49 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0.25102</v>
+        <v>0.249647</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.219048</v>
+        <v>0.213967</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.19347</v>
+        <v>0.185423</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.174287</v>
+        <v>0.164015</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>0.161499</v>
+        <v>0.149743</v>
       </c>
     </row>
     <row r="17">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>22501.1</v>
+        <v>29482.4</v>
       </c>
     </row>
     <row r="22">
